--- a/artfynd/A 28892-2026 artfynd.xlsx
+++ b/artfynd/A 28892-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,9 +790,5989 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135428693</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97511</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>53</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>630822</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6663148</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428693</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135428697</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97511</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>53</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>631033</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6663313</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428697</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135428698</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97511</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>53</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>631037</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6663307</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428698</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135428699</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97511</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>53</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>631049</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6663366</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428699</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135428701</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97511</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>53</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>631061</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6663407</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428701</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135428702</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97511</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>53</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>631046</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6663416</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428702</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135428706</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97511</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>53</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>631106</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6663445</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428706</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135428707</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97511</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>53</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>631122</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6663446</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428707</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135428713</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97511</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>53</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>631115</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6663490</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428713</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135428717</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97511</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>53</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>630991</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6663446</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428717</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135428718</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97511</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>53</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>630978</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6663443</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428718</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135428730</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97511</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>53</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>630764</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6663112</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428730</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135428737</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97511</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>53</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>630752</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6663078</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428737</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135428738</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97511</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>53</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>630767</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6663039</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428738</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135428683</v>
+      </c>
+      <c r="B17" t="n">
+        <v>85662</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>241</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gransotdyna</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Camarops tubulina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Shear</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>630837</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6663111</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428683</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135428694</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>630876</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6663262</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428694</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135428732</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92062</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>630764</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6663112</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428732</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135428691</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92721</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>630829</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6663154</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428691</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135428720</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92721</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>630855</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6663378</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428720</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135428721</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92721</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>630926</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6663286</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428721</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135428722</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92721</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>630858</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6663383</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428722</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135428704</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92069</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>631036</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6663467</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428704</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135428725</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92069</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>630747</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6663138</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428725</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135428681</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>630787</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6663042</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428681</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135428708</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>631141</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6663436</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428708</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135428726</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>630736</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6663129</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428726</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135428729</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>630749</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6663112</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428729</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135428687</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>630833</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6663128</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428687</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135428688</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>630828</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6663130</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428688</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135428696</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>631019</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6663297</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428696</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135428703</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>631050</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6663412</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428703</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135428719</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>630977</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6663438</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428719</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135428739</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>630772</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6663041</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428739</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135428735</v>
+      </c>
+      <c r="B36" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>630776</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6663091</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428735</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135428740</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>630787</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6663028</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428740</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135428686</v>
+      </c>
+      <c r="B38" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>630877</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6663083</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428686</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135428692</v>
+      </c>
+      <c r="B39" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>630829</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6663154</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428692</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135428695</v>
+      </c>
+      <c r="B40" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>631021</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6663270</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428695</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135428710</v>
+      </c>
+      <c r="B41" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>631111</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6663484</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428710</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135428700</v>
+      </c>
+      <c r="B42" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>631064</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6663377</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428700</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135428716</v>
+      </c>
+      <c r="B43" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>631071</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6663503</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428716</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135428734</v>
+      </c>
+      <c r="B44" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>630770</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6663096</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428734</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135428682</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>630860</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6663105</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428682</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135428705</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>631110</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6663442</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428705</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135428709</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>631148</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6663447</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428709</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135428711</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>631111</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6663491</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428711</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135428712</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>631115</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6663490</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428712</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135428714</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>631117</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6663489</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428714</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135428685</v>
+      </c>
+      <c r="B51" t="n">
+        <v>102020</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>223366</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Svarta vinbär</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ribes nigrum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>630838</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6663113</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428685</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135428690</v>
+      </c>
+      <c r="B52" t="n">
+        <v>92067</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6332881</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Risbosjön NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>630824</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6663153</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428690</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28892-2026 artfynd.xlsx
+++ b/artfynd/A 28892-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135428693</v>
       </c>
       <c r="B3" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135428697</v>
       </c>
       <c r="B4" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135428698</v>
       </c>
       <c r="B5" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>135428699</v>
       </c>
       <c r="B6" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>135428701</v>
       </c>
       <c r="B7" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>135428702</v>
       </c>
       <c r="B8" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>135428706</v>
       </c>
       <c r="B9" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>135428707</v>
       </c>
       <c r="B10" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>135428713</v>
       </c>
       <c r="B11" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>135428717</v>
       </c>
       <c r="B12" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135428718</v>
       </c>
       <c r="B13" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>135428730</v>
       </c>
       <c r="B14" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>135428737</v>
       </c>
       <c r="B15" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>135428738</v>
       </c>
       <c r="B16" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>135428694</v>
       </c>
       <c r="B18" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>135428732</v>
       </c>
       <c r="B19" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>135428691</v>
       </c>
       <c r="B20" t="n">
-        <v>92721</v>
+        <v>92723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>135428720</v>
       </c>
       <c r="B21" t="n">
-        <v>92721</v>
+        <v>92723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>135428721</v>
       </c>
       <c r="B22" t="n">
-        <v>92721</v>
+        <v>92723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>135428722</v>
       </c>
       <c r="B23" t="n">
-        <v>92721</v>
+        <v>92723</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>135428704</v>
       </c>
       <c r="B24" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>135428725</v>
       </c>
       <c r="B25" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>135428681</v>
       </c>
       <c r="B26" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>135428708</v>
       </c>
       <c r="B27" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>135428726</v>
       </c>
       <c r="B28" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>135428729</v>
       </c>
       <c r="B29" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>135428682</v>
       </c>
       <c r="B45" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>135428705</v>
       </c>
       <c r="B46" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>135428709</v>
       </c>
       <c r="B47" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>135428711</v>
       </c>
       <c r="B48" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>135428712</v>
       </c>
       <c r="B49" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>135428714</v>
       </c>
       <c r="B50" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>135428685</v>
       </c>
       <c r="B51" t="n">
-        <v>102020</v>
+        <v>102022</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>135428690</v>
       </c>
       <c r="B52" t="n">
-        <v>92067</v>
+        <v>92069</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 28892-2026 artfynd.xlsx
+++ b/artfynd/A 28892-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135428693</v>
       </c>
       <c r="B3" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135428697</v>
       </c>
       <c r="B4" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135428698</v>
       </c>
       <c r="B5" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>135428699</v>
       </c>
       <c r="B6" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>135428701</v>
       </c>
       <c r="B7" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>135428702</v>
       </c>
       <c r="B8" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>135428706</v>
       </c>
       <c r="B9" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>135428707</v>
       </c>
       <c r="B10" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>135428713</v>
       </c>
       <c r="B11" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>135428717</v>
       </c>
       <c r="B12" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135428718</v>
       </c>
       <c r="B13" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>135428730</v>
       </c>
       <c r="B14" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>135428737</v>
       </c>
       <c r="B15" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>135428738</v>
       </c>
       <c r="B16" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>135428683</v>
       </c>
       <c r="B17" t="n">
-        <v>85662</v>
+        <v>85664</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>135428694</v>
       </c>
       <c r="B18" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>135428732</v>
       </c>
       <c r="B19" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>135428691</v>
       </c>
       <c r="B20" t="n">
-        <v>92723</v>
+        <v>92738</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>135428720</v>
       </c>
       <c r="B21" t="n">
-        <v>92723</v>
+        <v>92738</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>135428721</v>
       </c>
       <c r="B22" t="n">
-        <v>92723</v>
+        <v>92738</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>135428722</v>
       </c>
       <c r="B23" t="n">
-        <v>92723</v>
+        <v>92738</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>135428704</v>
       </c>
       <c r="B24" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>135428725</v>
       </c>
       <c r="B25" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>135428681</v>
       </c>
       <c r="B26" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>135428708</v>
       </c>
       <c r="B27" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>135428726</v>
       </c>
       <c r="B28" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>135428729</v>
       </c>
       <c r="B29" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>135428687</v>
       </c>
       <c r="B30" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>135428688</v>
       </c>
       <c r="B31" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>135428696</v>
       </c>
       <c r="B32" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>135428703</v>
       </c>
       <c r="B33" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>135428719</v>
       </c>
       <c r="B34" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>135428739</v>
       </c>
       <c r="B35" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>135428735</v>
       </c>
       <c r="B36" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>135428740</v>
       </c>
       <c r="B37" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>135428686</v>
       </c>
       <c r="B38" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>135428692</v>
       </c>
       <c r="B39" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>135428695</v>
       </c>
       <c r="B40" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>135428710</v>
       </c>
       <c r="B41" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>135428700</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>8452</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>135428716</v>
       </c>
       <c r="B43" t="n">
-        <v>8450</v>
+        <v>8452</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>135428734</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>8452</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>135428682</v>
       </c>
       <c r="B45" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>135428705</v>
       </c>
       <c r="B46" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>135428709</v>
       </c>
       <c r="B47" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>135428711</v>
       </c>
       <c r="B48" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>135428712</v>
       </c>
       <c r="B49" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>135428714</v>
       </c>
       <c r="B50" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>135428685</v>
       </c>
       <c r="B51" t="n">
-        <v>102022</v>
+        <v>102039</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>135428690</v>
       </c>
       <c r="B52" t="n">
-        <v>92069</v>
+        <v>92083</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
